--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>82</v>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-description-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
